--- a/TestFiles/StatementProcessing/[MLB NEW]HappyFlowChangeCheckRunDate.xlsx
+++ b/TestFiles/StatementProcessing/[MLB NEW]HappyFlowChangeCheckRunDate.xlsx
@@ -79,7 +79,7 @@
     <t>Agent</t>
   </si>
   <si>
-    <t>DevaTest</t>
+    <t>test-DevaTest</t>
   </si>
   <si>
     <t>0987654321</t>
@@ -91,7 +91,7 @@
     <t>Integrity Health, LLC</t>
   </si>
   <si>
-    <t>IANG12370001IL262</t>
+    <t>IANG12370001IL269</t>
   </si>
   <si>
     <t>ROBERTS, PIPPIN</t>
@@ -659,7 +659,7 @@
         <v>28</v>
       </c>
       <c r="Q2" s="19">
-        <v>46441</v>
+        <v>46448</v>
       </c>
       <c r="R2" s="8" t="s">
         <v>29</v>
